--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3437,6 +3437,123 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129154374</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96902</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>53</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ormestorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>497099</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6417068</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96956</v>
+        <v>96958</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96962</v>
+        <v>96970</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -3442,7 +3442,7 @@
         <v>129154374</v>
       </c>
       <c r="B24" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 228-2024 artfynd.xlsx
+++ b/artfynd/A 228-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81793564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92910673</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93414664</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1180,6 +1200,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96696272</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,6 +1342,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96696412</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1454,6 +1484,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96696448</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1591,6 +1626,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798860</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1718,6 +1758,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103414030</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1845,6 +1890,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112740892</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1967,6 +2017,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119237552</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2084,6 +2139,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129154374</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2203,6 +2263,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96802033</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2323,6 +2388,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97231009</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2431,6 +2501,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99804264</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2539,6 +2614,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99806763</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2641,6 +2721,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106890061</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2753,6 +2838,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97316543</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2851,6 +2941,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112740163</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2962,6 +3057,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96852104</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3063,6 +3163,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73351271</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3184,6 +3289,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81793659</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3293,6 +3403,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95839298</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3414,6 +3529,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95020308</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3535,6 +3655,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103575984</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3656,6 +3781,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93261272</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3777,6 +3907,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93262851</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3893,6 +4028,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96902756</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4009,6 +4149,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105348599</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4124,6 +4269,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96414852</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4239,6 +4389,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96696735</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4354,6 +4509,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96786432</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4478,6 +4638,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96786609</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4578,6 +4743,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101249244</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4682,6 +4852,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102777420</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4797,6 +4972,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798060</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4916,6 +5096,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96831522</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5035,6 +5220,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96781710</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5154,6 +5344,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96807397</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5269,6 +5464,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96831470</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5388,6 +5588,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97119601</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5507,6 +5712,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96789472</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5626,6 +5836,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96796535</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5745,6 +5960,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96831483</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5864,6 +6084,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96887777</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5983,6 +6208,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97119599</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6102,6 +6332,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235056</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6215,6 +6450,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105348881</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6334,6 +6574,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96831488</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6453,6 +6698,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96831515</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6564,6 +6814,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102778380</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6675,6 +6930,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112742232</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6785,6 +7045,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112760321</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6904,6 +7169,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96693626</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6999,6 +7269,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103368043</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7107,6 +7382,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99174711</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7227,8 +7507,71 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102781301</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>